--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4EB157-578C-40E6-90A9-10930B806AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3340" yWindow="3340" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="GameModifiers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
   <si>
     <t>ModifierID</t>
   </si>
@@ -357,34 +359,57 @@
     <t>绑定AI思考器</t>
   </si>
   <si>
+    <t>CharacterCastSkill|ShootToTarget|3|MainCharacter|AimTarget</t>
+  </si>
+  <si>
+    <t>子弹生成</t>
+  </si>
+  <si>
+    <t>bool_set|IsFollowTarget|true</t>
+  </si>
+  <si>
+    <t>设置跟随状态</t>
+  </si>
+  <si>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|10</t>
+  </si>
+  <si>
     <t>碰撞时造成伤害</t>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|10</t>
-  </si>
-  <si>
-    <t>设置跟随状态</t>
-  </si>
-  <si>
-    <t>bool_set|IsFollowTarget|true</t>
-  </si>
-  <si>
-    <t>子弹生成</t>
-  </si>
-  <si>
-    <t>CharacterCastSkill|ShootToTarget|3|MainCharacter|AimTarget</t>
+    <t>CharacterCastSkill|GrabNearByObject|MainCharacter|Food;Tower</t>
+  </si>
+  <si>
+    <t>抓起附近的物品</t>
+  </si>
+  <si>
+    <t>CharacterCastSkill|DispelModifier|9001|MainCharacter</t>
+  </si>
+  <si>
+    <t>CharacterCastSkill|GrabNearByObject|MainCharacter</t>
+  </si>
+  <si>
+    <t>放下手里的物品</t>
+  </si>
+  <si>
+    <t>CharacterCastSkill|DispelModifier|10001|MainCharacter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -392,7 +417,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -400,16 +447,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -418,7 +471,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -427,31 +479,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -459,7 +486,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -468,7 +494,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -477,15 +502,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -494,24 +510,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -520,7 +525,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -528,14 +553,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -549,175 +566,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -727,6 +757,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -752,7 +797,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -787,15 +832,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -811,17 +847,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -837,131 +867,152 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -970,58 +1021,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1070,7 +1124,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1103,26 +1157,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1155,23 +1192,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1313,21 +1333,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E74"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="21.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="77.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1344,7 +1363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1361,7 +1380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1378,7 +1397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1395,7 +1414,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1412,7 +1431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1429,7 +1448,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1446,7 +1465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1463,7 +1482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1480,7 +1499,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1497,7 +1516,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1514,7 +1533,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>4</v>
       </c>
@@ -1531,7 +1550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1548,7 +1567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -1565,7 +1584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -1582,7 +1601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -1599,7 +1618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>1001</v>
       </c>
@@ -1616,7 +1635,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>1001</v>
       </c>
@@ -1633,7 +1652,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>1001</v>
       </c>
@@ -1650,7 +1669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1001</v>
       </c>
@@ -1667,7 +1686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1001</v>
       </c>
@@ -1684,7 +1703,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1701,7 +1720,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1718,7 +1737,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>1001</v>
       </c>
@@ -1735,7 +1754,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1001</v>
       </c>
@@ -1752,7 +1771,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>1002</v>
       </c>
@@ -1769,7 +1788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>1002</v>
       </c>
@@ -1786,7 +1805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>1002</v>
       </c>
@@ -1803,7 +1822,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>1002</v>
       </c>
@@ -1820,7 +1839,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>1002</v>
       </c>
@@ -1837,7 +1856,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>1002</v>
       </c>
@@ -1854,7 +1873,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>1002</v>
       </c>
@@ -1871,7 +1890,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>1002</v>
       </c>
@@ -1888,7 +1907,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>1002</v>
       </c>
@@ -1905,7 +1924,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1922,7 +1941,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1939,7 +1958,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>1003</v>
       </c>
@@ -1956,7 +1975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>1003</v>
       </c>
@@ -1973,7 +1992,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>1003</v>
       </c>
@@ -1990,7 +2009,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>1003</v>
       </c>
@@ -2007,7 +2026,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>1003</v>
       </c>
@@ -2024,7 +2043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>1003</v>
       </c>
@@ -2041,7 +2060,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>1003</v>
       </c>
@@ -2058,7 +2077,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>1003</v>
       </c>
@@ -2075,7 +2094,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>1003</v>
       </c>
@@ -2092,7 +2111,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>1003</v>
       </c>
@@ -2109,7 +2128,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>1003</v>
       </c>
@@ -2126,7 +2145,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>1004</v>
       </c>
@@ -2143,7 +2162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>1004</v>
       </c>
@@ -2160,7 +2179,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>1004</v>
       </c>
@@ -2177,7 +2196,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>1004</v>
       </c>
@@ -2194,7 +2213,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>1004</v>
       </c>
@@ -2211,7 +2230,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -2228,7 +2247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>1004</v>
       </c>
@@ -2245,7 +2264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>1004</v>
       </c>
@@ -2262,7 +2281,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>3001</v>
       </c>
@@ -2279,7 +2298,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>3001</v>
       </c>
@@ -2296,7 +2315,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>3001</v>
       </c>
@@ -2313,7 +2332,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>3002</v>
       </c>
@@ -2330,7 +2349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>3002</v>
       </c>
@@ -2347,7 +2366,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>3002</v>
       </c>
@@ -2364,7 +2383,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>4001</v>
       </c>
@@ -2381,7 +2400,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>4001</v>
       </c>
@@ -2398,7 +2417,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>4002</v>
       </c>
@@ -2415,7 +2434,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>4002</v>
       </c>
@@ -2432,7 +2451,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>4002</v>
       </c>
@@ -2449,7 +2468,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>4002</v>
       </c>
@@ -2466,7 +2485,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>5001</v>
       </c>
@@ -2483,7 +2502,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>5001</v>
       </c>
@@ -2500,7 +2519,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>6001</v>
       </c>
@@ -2517,7 +2536,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>6001</v>
       </c>
@@ -2534,7 +2553,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>7001</v>
       </c>
@@ -2545,13 +2564,13 @@
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>8001</v>
       </c>
@@ -2562,13 +2581,13 @@
         <v>5</v>
       </c>
       <c r="D73" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73" t="s">
         <v>113</v>
       </c>
-      <c r="E73" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>8001</v>
       </c>
@@ -2579,14 +2598,82 @@
         <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>110</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>9001</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" t="s">
+        <v>116</v>
+      </c>
+      <c r="E75" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>9001</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>10001</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" t="s">
+        <v>119</v>
+      </c>
+      <c r="E77" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>10001</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" t="s">
+        <v>121</v>
+      </c>
+      <c r="E78" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="124">
   <si>
     <t>ModifierID</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>碰撞时造成伤害</t>
+  </si>
+  <si>
+    <t>CharacterHitTarget|DoDamage|DoHitCharacter|9999</t>
+  </si>
+  <si>
+    <t>碰撞时摧毁自身</t>
   </si>
   <si>
     <t>CharacterCastSkill|GrabNearByObject|MainCharacter|Food;Tower</t>
@@ -405,14 +411,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,79 +870,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -955,7 +954,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -967,7 +966,7 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -979,7 +978,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -991,7 +990,7 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1003,7 +1002,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1339,7 +1338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="21.4166666666667" customWidth="1"/>
@@ -2606,10 +2605,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>9001</v>
+        <v>8001</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" t="s">
         <v>32</v>
@@ -2626,7 +2625,7 @@
         <v>9001</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
@@ -2635,24 +2634,24 @@
         <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>10001</v>
+        <v>9001</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
       </c>
       <c r="D77" t="s">
+        <v>120</v>
+      </c>
+      <c r="E77" t="s">
         <v>119</v>
-      </c>
-      <c r="E77" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2660,7 +2659,7 @@
         <v>10001</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
@@ -2669,7 +2668,24 @@
         <v>121</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>10001</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s">
+        <v>123</v>
+      </c>
+      <c r="E79" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -383,7 +383,7 @@
     <t>碰撞时摧毁自身</t>
   </si>
   <si>
-    <t>CharacterCastSkill|GrabNearByObject|MainCharacter|Food;Tower</t>
+    <t>CharacterCastSkill|GrabNearByObject|MainCharacter|Dish</t>
   </si>
   <si>
     <t>抓起附近的物品</t>
@@ -392,7 +392,7 @@
     <t>CharacterCastSkill|DispelModifier|9001|MainCharacter</t>
   </si>
   <si>
-    <t>CharacterCastSkill|GrabNearByObject|MainCharacter</t>
+    <t>CharacterCastSkill|DropCurObject|MainCharacter</t>
   </si>
   <si>
     <t>放下手里的物品</t>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
   <si>
     <t>ModifierID</t>
   </si>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>CharacterCastSkill|DispelModifier|10001|MainCharacter</t>
+  </si>
+  <si>
+    <t>烹饪中，设置特效</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="21.4166666666667" customWidth="1"/>
@@ -2688,6 +2691,23 @@
         <v>122</v>
       </c>
     </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>11001</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F124303-A4DB-4FCB-B48D-F1B2B3B8AC38}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameModifiers" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="126">
   <si>
     <t>ModifierID</t>
   </si>
@@ -402,19 +395,17 @@
   </si>
   <si>
     <t>烹饪中，设置特效</t>
+  </si>
+  <si>
+    <t>CharacterCastSkill|DispelModifier|7001|MainCharacter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,337 +414,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线 Light"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -761,323 +445,31 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1335,20 +727,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="21.4140625" customWidth="1"/>
     <col min="4" max="4" width="77.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1382,7 +774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1399,7 +791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1416,7 +808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1433,7 +825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1450,7 +842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1467,7 +859,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1484,7 +876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1501,7 +893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1518,7 +910,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1535,7 +927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
@@ -1552,7 +944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1569,7 +961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -1586,7 +978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -1603,7 +995,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -1620,7 +1012,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1001</v>
       </c>
@@ -1637,7 +1029,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1001</v>
       </c>
@@ -1654,7 +1046,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1001</v>
       </c>
@@ -1671,7 +1063,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1001</v>
       </c>
@@ -1688,7 +1080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1001</v>
       </c>
@@ -1705,7 +1097,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1722,7 +1114,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1739,7 +1131,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1001</v>
       </c>
@@ -1756,7 +1148,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1001</v>
       </c>
@@ -1773,7 +1165,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1002</v>
       </c>
@@ -1790,7 +1182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1002</v>
       </c>
@@ -1807,7 +1199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1002</v>
       </c>
@@ -1824,7 +1216,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1002</v>
       </c>
@@ -1841,7 +1233,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1002</v>
       </c>
@@ -1858,7 +1250,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1002</v>
       </c>
@@ -1875,7 +1267,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1002</v>
       </c>
@@ -1892,7 +1284,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1002</v>
       </c>
@@ -1909,7 +1301,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1002</v>
       </c>
@@ -1926,7 +1318,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1943,7 +1335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1960,7 +1352,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1003</v>
       </c>
@@ -1977,7 +1369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1003</v>
       </c>
@@ -1994,7 +1386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1003</v>
       </c>
@@ -2011,7 +1403,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1003</v>
       </c>
@@ -2028,7 +1420,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1003</v>
       </c>
@@ -2045,7 +1437,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1003</v>
       </c>
@@ -2062,7 +1454,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1003</v>
       </c>
@@ -2079,7 +1471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1003</v>
       </c>
@@ -2096,7 +1488,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1003</v>
       </c>
@@ -2113,7 +1505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1003</v>
       </c>
@@ -2130,7 +1522,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1003</v>
       </c>
@@ -2147,7 +1539,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1004</v>
       </c>
@@ -2164,7 +1556,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1004</v>
       </c>
@@ -2181,7 +1573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1004</v>
       </c>
@@ -2198,7 +1590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1004</v>
       </c>
@@ -2215,7 +1607,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1004</v>
       </c>
@@ -2232,7 +1624,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -2249,7 +1641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1004</v>
       </c>
@@ -2266,7 +1658,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1004</v>
       </c>
@@ -2283,7 +1675,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>3001</v>
       </c>
@@ -2300,7 +1692,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>3001</v>
       </c>
@@ -2317,7 +1709,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>3001</v>
       </c>
@@ -2334,7 +1726,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>3002</v>
       </c>
@@ -2351,7 +1743,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>3002</v>
       </c>
@@ -2368,7 +1760,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>3002</v>
       </c>
@@ -2385,7 +1777,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>4001</v>
       </c>
@@ -2402,7 +1794,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>4001</v>
       </c>
@@ -2419,7 +1811,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>4002</v>
       </c>
@@ -2436,7 +1828,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>4002</v>
       </c>
@@ -2453,7 +1845,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>4002</v>
       </c>
@@ -2470,7 +1862,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>4002</v>
       </c>
@@ -2487,7 +1879,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>5001</v>
       </c>
@@ -2504,7 +1896,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>5001</v>
       </c>
@@ -2521,7 +1913,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>6001</v>
       </c>
@@ -2538,7 +1930,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>6001</v>
       </c>
@@ -2555,7 +1947,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>7001</v>
       </c>
@@ -2572,144 +1964,162 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>8001</v>
+        <v>7001</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" t="s">
-        <v>112</v>
+        <v>32</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="E73" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8001</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E74" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8001</v>
       </c>
       <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" t="s">
+        <v>114</v>
+      </c>
+      <c r="E75" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>8001</v>
+      </c>
+      <c r="B76">
         <v>3</v>
       </c>
-      <c r="C75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
         <v>116</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
-      <c r="A76">
-        <v>9001</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" t="s">
-        <v>118</v>
-      </c>
-      <c r="E76" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9001</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E77" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>10001</v>
+        <v>9001</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E78" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>10001</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E79" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
+        <v>10001</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" t="s">
+        <v>123</v>
+      </c>
+      <c r="E80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>11001</v>
       </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
         <v>12</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D81" t="s">
         <v>13</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E81" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F124303-A4DB-4FCB-B48D-F1B2B3B8AC38}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEC1257-84B6-45F2-9ECD-DBD55820C993}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,9 +364,6 @@
     <t>设置跟随状态</t>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|10</t>
-  </si>
-  <si>
     <t>碰撞时造成伤害</t>
   </si>
   <si>
@@ -398,6 +395,10 @@
   </si>
   <si>
     <t>CharacterCastSkill|DispelModifier|7001|MainCharacter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1975,10 +1976,10 @@
         <v>32</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2008,11 +2009,11 @@
       <c r="C75" t="s">
         <v>32</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E75" t="s">
         <v>114</v>
-      </c>
-      <c r="E75" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,10 +2027,10 @@
         <v>32</v>
       </c>
       <c r="D76" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" t="s">
         <v>116</v>
-      </c>
-      <c r="E76" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2043,10 +2044,10 @@
         <v>32</v>
       </c>
       <c r="D77" t="s">
+        <v>117</v>
+      </c>
+      <c r="E77" t="s">
         <v>118</v>
-      </c>
-      <c r="E77" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2060,10 +2061,10 @@
         <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2077,10 +2078,10 @@
         <v>32</v>
       </c>
       <c r="D79" t="s">
+        <v>120</v>
+      </c>
+      <c r="E79" t="s">
         <v>121</v>
-      </c>
-      <c r="E79" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2094,10 +2095,10 @@
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2114,7 +2115,7 @@
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEC1257-84B6-45F2-9ECD-DBD55820C993}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE16811-78D7-4FCE-A85D-66417DC2FE48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,7 +398,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|40</t>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE16811-78D7-4FCE-A85D-66417DC2FE48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E171FC3E-A3D2-4664-B6E2-A3740244561D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
   <si>
     <t>ModifierID</t>
   </si>
@@ -399,6 +399,14 @@
   </si>
   <si>
     <t>CharacterHitTarget|DoDamage|BeHitCharacter|18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|Reduce_HP_PerSecond|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒掉血Buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="21.4140625" customWidth="1"/>
@@ -2118,6 +2126,23 @@
         <v>123</v>
       </c>
     </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>12001</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E171FC3E-A3D2-4664-B6E2-A3740244561D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971F99A2-4915-4B74-9B22-52D91D2E2987}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,15 +398,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|18</t>
+    <t>每秒掉血Buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>float_add|Reduce_HP_PerSecond|3</t>
+    <t>float_add|Reduce_MP_PerSecond|3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每秒掉血Buff</t>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2018,7 +2018,7 @@
         <v>32</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
         <v>114</v>
@@ -2140,7 +2140,7 @@
         <v>126</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971F99A2-4915-4B74-9B22-52D91D2E2987}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C04E0F4-C3D9-4266-A7B1-8945A53CECE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="9570" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="GameModifiers" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="132">
   <si>
     <t>ModifierID</t>
   </si>
@@ -358,12 +363,21 @@
     <t>子弹生成</t>
   </si>
   <si>
+    <t>CharacterCastSkill|DispelModifier|7001|MainCharacter</t>
+  </si>
+  <si>
+    <t>抓起附近的物品</t>
+  </si>
+  <si>
     <t>bool_set|IsFollowTarget|true</t>
   </si>
   <si>
     <t>设置跟随状态</t>
   </si>
   <si>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|1</t>
+  </si>
+  <si>
     <t>碰撞时造成伤害</t>
   </si>
   <si>
@@ -376,9 +390,6 @@
     <t>CharacterCastSkill|GrabNearByObject|MainCharacter|Dish</t>
   </si>
   <si>
-    <t>抓起附近的物品</t>
-  </si>
-  <si>
     <t>CharacterCastSkill|DispelModifier|9001|MainCharacter</t>
   </si>
   <si>
@@ -394,19 +405,25 @@
     <t>烹饪中，设置特效</t>
   </si>
   <si>
-    <t>CharacterCastSkill|DispelModifier|7001|MainCharacter</t>
+    <t>float_add|Reduce_MP_PerSecond|3</t>
+  </si>
+  <si>
+    <t>每秒掉血Buff</t>
+  </si>
+  <si>
+    <t>float_add|Reduce_MP_PerSecond|-30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每秒掉血Buff</t>
+    <t>每秒回血Buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>float_add|Reduce_MP_PerSecond|3</t>
+    <t>int_add|Damage_Shoot|10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|1</t>
+    <t>加伤害Buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -414,28 +431,34 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -460,11 +483,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +553,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -560,9 +586,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -595,6 +638,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -737,1410 +797,1450 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E82"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F163EA-9459-48C1-AF83-EE818DD292D1}">
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="21.4140625" customWidth="1"/>
-    <col min="4" max="4" width="77.75" customWidth="1"/>
+    <col min="1" max="3" width="22.4140625" customWidth="1"/>
+    <col min="4" max="4" width="80.58203125" customWidth="1"/>
+    <col min="5" max="5" width="22.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="A13" s="1">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>2001</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>2001</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>2001</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>1001</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>1001</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>1001</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>3</v>
       </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>1001</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>4</v>
       </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>1001</v>
       </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="B21" s="1">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>1001</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>6</v>
       </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>1001</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>7</v>
       </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>1001</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>8</v>
       </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>1001</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>9</v>
       </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>1002</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>1002</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>1002</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>1002</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>4</v>
       </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="1">
         <v>1002</v>
       </c>
-      <c r="B30">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B30" s="1">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>1002</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>6</v>
       </c>
-      <c r="C31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="1">
         <v>1002</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>7</v>
       </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="1">
         <v>1002</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>8</v>
       </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="1">
         <v>1002</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>9</v>
       </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="1">
         <v>1002</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>10</v>
       </c>
-      <c r="C35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="1">
         <v>1002</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>11</v>
       </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="1">
         <v>1003</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="1">
         <v>1003</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>2</v>
       </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="1">
         <v>1003</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>3</v>
       </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="1">
         <v>1003</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>4</v>
       </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="A41" s="1">
         <v>1003</v>
       </c>
-      <c r="B41">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="B41" s="1">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="1">
         <v>1003</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="1">
         <v>6</v>
       </c>
-      <c r="C42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="1">
         <v>1003</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="1">
         <v>7</v>
       </c>
-      <c r="C43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="1">
         <v>1003</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="1">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="1">
         <v>1003</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1">
         <v>9</v>
       </c>
-      <c r="C45" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="1">
         <v>1003</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1">
         <v>10</v>
       </c>
-      <c r="C46" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="1">
         <v>1003</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="1">
         <v>11</v>
       </c>
-      <c r="C47" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="1">
         <v>1004</v>
       </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="A49" s="1">
         <v>1004</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1">
         <v>2</v>
       </c>
-      <c r="C49" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="A50" s="1">
         <v>1004</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1">
         <v>3</v>
       </c>
-      <c r="C50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="A51" s="1">
         <v>1004</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="1">
         <v>4</v>
       </c>
-      <c r="C51" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="A52" s="1">
         <v>1004</v>
       </c>
-      <c r="B52">
-        <v>5</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="B52" s="1">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="A53" s="1">
         <v>1004</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="1">
         <v>6</v>
       </c>
-      <c r="C53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="A54" s="1">
         <v>1004</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="1">
         <v>7</v>
       </c>
-      <c r="C54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="A55" s="1">
         <v>1004</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1">
         <v>8</v>
       </c>
-      <c r="C55" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="A56" s="1">
         <v>3001</v>
       </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="A57" s="1">
         <v>3001</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1">
         <v>2</v>
       </c>
-      <c r="C57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="A58" s="1">
         <v>3001</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1">
         <v>3</v>
       </c>
-      <c r="C58" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="A59" s="1">
         <v>3002</v>
       </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="A60" s="1">
         <v>3002</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1">
         <v>2</v>
       </c>
-      <c r="C60" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="A61" s="1">
         <v>3002</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1">
         <v>3</v>
       </c>
-      <c r="C61" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="A62" s="1">
         <v>4001</v>
       </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="A63" s="1">
         <v>4001</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1">
         <v>2</v>
       </c>
-      <c r="C63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="C63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="A64" s="1">
         <v>4002</v>
       </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="A65" s="1">
         <v>4002</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1">
         <v>2</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="A66" s="1">
         <v>4002</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="1">
         <v>3</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="A67" s="1">
         <v>4002</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="1">
         <v>4</v>
       </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="A68" s="1">
         <v>5001</v>
       </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="B68" s="1">
+        <v>1</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="A69" s="1">
         <v>5001</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="1">
         <v>2</v>
       </c>
-      <c r="C69" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="A70" s="1">
         <v>6001</v>
       </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="A71" s="1">
         <v>6001</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="1">
         <v>2</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72">
+      <c r="A72" s="1">
         <v>7001</v>
       </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73">
+      <c r="A73" s="1">
         <v>7001</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="1">
         <v>2</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>8001</v>
+      </c>
+      <c r="B74" s="1">
+        <v>1</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>8001</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>8001</v>
+      </c>
+      <c r="B76" s="1">
+        <v>3</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>9001</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>9001</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>10001</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>10001</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E73" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>8001</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" t="s">
-        <v>112</v>
-      </c>
-      <c r="E74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>8001</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E75" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>8001</v>
-      </c>
-      <c r="B76">
-        <v>3</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" t="s">
-        <v>115</v>
-      </c>
-      <c r="E76" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>9001</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" t="s">
-        <v>117</v>
-      </c>
-      <c r="E77" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>9001</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78" t="s">
-        <v>32</v>
-      </c>
-      <c r="D78" t="s">
-        <v>119</v>
-      </c>
-      <c r="E78" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>10001</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79" t="s">
-        <v>32</v>
-      </c>
-      <c r="D79" t="s">
-        <v>120</v>
-      </c>
-      <c r="E79" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>10001</v>
-      </c>
-      <c r="B80">
-        <v>2</v>
-      </c>
-      <c r="C80" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" t="s">
-        <v>122</v>
-      </c>
-      <c r="E80" t="s">
-        <v>121</v>
+      <c r="E80" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="A81" s="1">
         <v>11001</v>
       </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B81" s="1">
+        <v>1</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E81" t="s">
-        <v>123</v>
+      <c r="E81" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="A82" s="1">
         <v>12001</v>
       </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" s="1">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>126</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>13001</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>14001</v>
+      </c>
+      <c r="B84" s="2">
+        <v>1</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9998AD57-08CA-476C-A5F4-26645839CBE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AA9BEE-7B92-40F1-BAAA-2FB0633B94D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="9570" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
@@ -534,11 +534,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>int_set|myAttackSkillID|10</t>
+    <t>CharacterCastSkill|DispelModifier|16001|MainCharacter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterCastSkill|DispelModifier|16001|MainCharacter</t>
+    <t>int_set|myAttackSkillID|5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2350,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E85" t="s">
         <v>131</v>
@@ -2690,7 +2690,7 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E105" t="s">
         <v>112</v>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AA9BEE-7B92-40F1-BAAA-2FB0633B94D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E10E40-E171-4D26-8F8D-39362ACC4F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="9570" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,33 +402,15 @@
     <t>烹饪中，设置特效</t>
   </si>
   <si>
-    <t>float_add|Reduce_MP_PerSecond|3</t>
-  </si>
-  <si>
-    <t>float_add|Reduce_MP_PerSecond|1.5</t>
-  </si>
-  <si>
-    <t>基础塔：每秒消耗1.5点MP</t>
-  </si>
-  <si>
     <t>int_set|myAttackSkillID|5</t>
   </si>
   <si>
     <t>基础塔：设置攻击技能为生成子弹</t>
   </si>
   <si>
-    <t>散射塔：每秒消耗3点MP（加倍）</t>
-  </si>
-  <si>
     <t>散射塔：设置攻击技能为散射攻击</t>
   </si>
   <si>
-    <t>float_add|Reduce_MP_PerSecond|0.75</t>
-  </si>
-  <si>
-    <t>减速塔：每秒消耗0.75点MP（减半）</t>
-  </si>
-  <si>
     <t>减速塔：设置攻击技能为减速攻击</t>
   </si>
   <si>
@@ -442,9 +424,6 @@
   </si>
   <si>
     <t>散射攻击：技能使用后驱散</t>
-  </si>
-  <si>
-    <t>float_add|Reduce_MP_PerSecond|-30</t>
   </si>
   <si>
     <t>每秒回血Buff</t>
@@ -539,6 +518,138 @@
   </si>
   <si>
     <t>int_set|myAttackSkillID|5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|Reduce_MP_PerSecond|1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>float_add|Reduce_MP_PerSecond|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>float_add|Reduce_MP_PerSecond|0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>基</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>础</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>塔：每秒消耗1点MP</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>散射塔：每秒消耗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>点MP（加倍）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>减速塔：每秒消耗0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>点MP（减半）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>float_add|Reduce_MP_PerSecond|-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>50</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,21 +657,42 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -607,9 +739,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -647,7 +779,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -753,7 +885,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -895,7 +1027,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -904,14 +1036,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F163EA-9459-48C1-AF83-EE818DD292D1}">
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="3" width="22.4140625" customWidth="1"/>
-    <col min="4" max="4" width="80.58203125" customWidth="1"/>
-    <col min="5" max="5" width="22.4140625" customWidth="1"/>
+    <col min="1" max="3" width="22.3984375" customWidth="1"/>
+    <col min="4" max="4" width="80.59765625" customWidth="1"/>
+    <col min="5" max="5" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -928,7 +1060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -945,7 +1077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -962,7 +1094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -979,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -996,7 +1128,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1013,7 +1145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1030,7 +1162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1047,7 +1179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1064,7 +1196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1081,7 +1213,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1098,7 +1230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>4</v>
       </c>
@@ -1115,7 +1247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1132,7 +1264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -1149,7 +1281,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -1166,7 +1298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -1183,7 +1315,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>1001</v>
       </c>
@@ -1200,7 +1332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>1001</v>
       </c>
@@ -1217,7 +1349,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>1001</v>
       </c>
@@ -1234,7 +1366,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1001</v>
       </c>
@@ -1251,7 +1383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1001</v>
       </c>
@@ -1268,7 +1400,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1285,7 +1417,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1302,7 +1434,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>1001</v>
       </c>
@@ -1319,7 +1451,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1001</v>
       </c>
@@ -1336,7 +1468,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>1002</v>
       </c>
@@ -1353,7 +1485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>1002</v>
       </c>
@@ -1370,7 +1502,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>1002</v>
       </c>
@@ -1387,7 +1519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>1002</v>
       </c>
@@ -1404,7 +1536,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>1002</v>
       </c>
@@ -1421,7 +1553,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>1002</v>
       </c>
@@ -1438,7 +1570,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>1002</v>
       </c>
@@ -1455,7 +1587,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>1002</v>
       </c>
@@ -1472,7 +1604,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>1002</v>
       </c>
@@ -1489,7 +1621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1506,7 +1638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1523,7 +1655,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>1003</v>
       </c>
@@ -1540,7 +1672,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>1003</v>
       </c>
@@ -1557,7 +1689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>1003</v>
       </c>
@@ -1574,7 +1706,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>1003</v>
       </c>
@@ -1591,7 +1723,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>1003</v>
       </c>
@@ -1608,7 +1740,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>1003</v>
       </c>
@@ -1625,7 +1757,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>1003</v>
       </c>
@@ -1642,7 +1774,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>1003</v>
       </c>
@@ -1659,7 +1791,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>1003</v>
       </c>
@@ -1676,7 +1808,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>1003</v>
       </c>
@@ -1693,7 +1825,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>1003</v>
       </c>
@@ -1710,7 +1842,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>1004</v>
       </c>
@@ -1727,7 +1859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>1004</v>
       </c>
@@ -1744,7 +1876,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>1004</v>
       </c>
@@ -1761,7 +1893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>1004</v>
       </c>
@@ -1778,7 +1910,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>1004</v>
       </c>
@@ -1795,7 +1927,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -1812,7 +1944,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>1004</v>
       </c>
@@ -1829,7 +1961,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>1004</v>
       </c>
@@ -1846,7 +1978,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>3001</v>
       </c>
@@ -1863,7 +1995,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>3001</v>
       </c>
@@ -1874,13 +2006,13 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>3001</v>
       </c>
@@ -1897,7 +2029,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>3002</v>
       </c>
@@ -1914,7 +2046,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>3002</v>
       </c>
@@ -1931,7 +2063,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>3002</v>
       </c>
@@ -1948,7 +2080,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>4001</v>
       </c>
@@ -1965,7 +2097,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>4001</v>
       </c>
@@ -1982,7 +2114,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>4002</v>
       </c>
@@ -1999,7 +2131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>4002</v>
       </c>
@@ -2016,7 +2148,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>4002</v>
       </c>
@@ -2033,7 +2165,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>4002</v>
       </c>
@@ -2050,7 +2182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>5001</v>
       </c>
@@ -2067,7 +2199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>5001</v>
       </c>
@@ -2084,7 +2216,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>6001</v>
       </c>
@@ -2101,7 +2233,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>6001</v>
       </c>
@@ -2118,7 +2250,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>7001</v>
       </c>
@@ -2135,7 +2267,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>7001</v>
       </c>
@@ -2152,7 +2284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>8001</v>
       </c>
@@ -2169,7 +2301,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>8001</v>
       </c>
@@ -2186,7 +2318,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>8001</v>
       </c>
@@ -2203,7 +2335,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>9001</v>
       </c>
@@ -2220,7 +2352,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>9001</v>
       </c>
@@ -2237,7 +2369,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>10001</v>
       </c>
@@ -2254,7 +2386,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>10001</v>
       </c>
@@ -2271,7 +2403,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>11001</v>
       </c>
@@ -2288,7 +2420,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>12001</v>
       </c>
@@ -2299,13 +2431,13 @@
         <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>12001</v>
       </c>
@@ -2316,13 +2448,13 @@
         <v>5</v>
       </c>
       <c r="D83" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>12002</v>
       </c>
@@ -2333,13 +2465,13 @@
         <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="E84" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>12002</v>
       </c>
@@ -2350,13 +2482,13 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E85" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>12003</v>
       </c>
@@ -2367,13 +2499,13 @@
         <v>5</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>12003</v>
       </c>
@@ -2384,13 +2516,13 @@
         <v>5</v>
       </c>
       <c r="D87" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>13001</v>
       </c>
@@ -2401,13 +2533,13 @@
         <v>32</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E88" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>13001</v>
       </c>
@@ -2418,13 +2550,13 @@
         <v>32</v>
       </c>
       <c r="D89" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E89" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>13001</v>
       </c>
@@ -2435,13 +2567,13 @@
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>14001</v>
       </c>
@@ -2452,13 +2584,13 @@
         <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E91" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>14001</v>
       </c>
@@ -2469,13 +2601,13 @@
         <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E92" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>14002</v>
       </c>
@@ -2486,13 +2618,13 @@
         <v>32</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E93" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>14002</v>
       </c>
@@ -2503,13 +2635,13 @@
         <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E94" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>15001</v>
       </c>
@@ -2520,13 +2652,13 @@
         <v>5</v>
       </c>
       <c r="D95" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E95" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>15001</v>
       </c>
@@ -2537,13 +2669,13 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E96" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>8002</v>
       </c>
@@ -2560,7 +2692,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>8002</v>
       </c>
@@ -2571,13 +2703,13 @@
         <v>32</v>
       </c>
       <c r="D98" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>8002</v>
       </c>
@@ -2594,7 +2726,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>8003</v>
       </c>
@@ -2611,7 +2743,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>8003</v>
       </c>
@@ -2622,13 +2754,13 @@
         <v>32</v>
       </c>
       <c r="D101" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E101" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>8003</v>
       </c>
@@ -2645,7 +2777,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>12004</v>
       </c>
@@ -2656,13 +2788,13 @@
         <v>5</v>
       </c>
       <c r="D103" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E103" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>16001</v>
       </c>
@@ -2673,13 +2805,13 @@
         <v>32</v>
       </c>
       <c r="D104" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E104" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>16001</v>
       </c>
@@ -2690,13 +2822,13 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E105" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>16002</v>
       </c>
@@ -2707,13 +2839,13 @@
         <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E106" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>16002</v>
       </c>
@@ -2724,13 +2856,13 @@
         <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E107" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>16002</v>
       </c>
@@ -2741,13 +2873,13 @@
         <v>32</v>
       </c>
       <c r="D108" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E108" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>16002</v>
       </c>
@@ -2764,7 +2896,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>16003</v>
       </c>
@@ -2775,10 +2907,10 @@
         <v>5</v>
       </c>
       <c r="D110" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E110" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E10E40-E171-4D26-8F8D-39362ACC4F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E3FA3A-0F4A-45C8-AF4F-DDCD937DC092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="170">
   <si>
     <t>ModifierID</t>
   </si>
@@ -388,9 +388,6 @@
   </si>
   <si>
     <t>CharacterCastSkill|DispelModifier|9001|MainCharacter</t>
-  </si>
-  <si>
-    <t>CharacterCastSkill|DropCurObject|MainCharacter</t>
   </si>
   <si>
     <t>放下手里的物品</t>
@@ -498,10 +495,6 @@
   </si>
   <si>
     <t>CharacterHitTarget|AddModifier|16003|BeHitCharacter|1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float_add|MaxSpeed|-0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -650,6 +643,46 @@
       </rPr>
       <t>50</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>float_add|MaxSpeed|-0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterCastSkill|DropCurObject|MainCharacter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CharacterHitTarget|DoDamage|BeHitCharacter|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>36</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterHitTarget|DoDamage|DoHitCharacter|9999</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2006,7 +2039,7 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E57" t="s">
         <v>84</v>
@@ -2380,10 +2413,10 @@
         <v>32</v>
       </c>
       <c r="D79" t="s">
+        <v>167</v>
+      </c>
+      <c r="E79" t="s">
         <v>121</v>
-      </c>
-      <c r="E79" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2397,10 +2430,10 @@
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2417,7 +2450,7 @@
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2431,10 +2464,10 @@
         <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2448,10 +2481,10 @@
         <v>5</v>
       </c>
       <c r="D83" t="s">
+        <v>124</v>
+      </c>
+      <c r="E83" t="s">
         <v>125</v>
-      </c>
-      <c r="E83" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2465,10 +2498,10 @@
         <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E84" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2482,10 +2515,10 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2499,10 +2532,10 @@
         <v>5</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2516,10 +2549,10 @@
         <v>5</v>
       </c>
       <c r="D87" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2533,10 +2566,10 @@
         <v>32</v>
       </c>
       <c r="D88" t="s">
+        <v>128</v>
+      </c>
+      <c r="E88" t="s">
         <v>129</v>
-      </c>
-      <c r="E88" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2550,10 +2583,10 @@
         <v>32</v>
       </c>
       <c r="D89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E89" t="s">
         <v>131</v>
-      </c>
-      <c r="E89" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2567,10 +2600,10 @@
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2584,10 +2617,10 @@
         <v>32</v>
       </c>
       <c r="D91" t="s">
+        <v>133</v>
+      </c>
+      <c r="E91" t="s">
         <v>134</v>
-      </c>
-      <c r="E91" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2601,10 +2634,10 @@
         <v>32</v>
       </c>
       <c r="D92" t="s">
+        <v>135</v>
+      </c>
+      <c r="E92" t="s">
         <v>136</v>
-      </c>
-      <c r="E92" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2618,10 +2651,10 @@
         <v>32</v>
       </c>
       <c r="D93" t="s">
+        <v>137</v>
+      </c>
+      <c r="E93" t="s">
         <v>138</v>
-      </c>
-      <c r="E93" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2635,10 +2668,10 @@
         <v>32</v>
       </c>
       <c r="D94" t="s">
+        <v>139</v>
+      </c>
+      <c r="E94" t="s">
         <v>140</v>
-      </c>
-      <c r="E94" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2652,10 +2685,10 @@
         <v>5</v>
       </c>
       <c r="D95" t="s">
+        <v>141</v>
+      </c>
+      <c r="E95" t="s">
         <v>142</v>
-      </c>
-      <c r="E95" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2669,10 +2702,10 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
+        <v>143</v>
+      </c>
+      <c r="E96" t="s">
         <v>144</v>
-      </c>
-      <c r="E96" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2703,10 +2736,10 @@
         <v>32</v>
       </c>
       <c r="D98" t="s">
+        <v>145</v>
+      </c>
+      <c r="E98" t="s">
         <v>146</v>
-      </c>
-      <c r="E98" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2754,10 +2787,10 @@
         <v>32</v>
       </c>
       <c r="D101" t="s">
+        <v>168</v>
+      </c>
+      <c r="E101" t="s">
         <v>146</v>
-      </c>
-      <c r="E101" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2771,7 +2804,7 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="E102" t="s">
         <v>118</v>
@@ -2788,10 +2821,10 @@
         <v>5</v>
       </c>
       <c r="D103" t="s">
+        <v>147</v>
+      </c>
+      <c r="E103" t="s">
         <v>148</v>
-      </c>
-      <c r="E103" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2805,7 +2838,7 @@
         <v>32</v>
       </c>
       <c r="D104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E104" t="s">
         <v>110</v>
@@ -2822,7 +2855,7 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
         <v>112</v>
@@ -2839,7 +2872,7 @@
         <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E106" t="s">
         <v>114</v>
@@ -2856,7 +2889,7 @@
         <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E107" t="s">
         <v>116</v>
@@ -2873,10 +2906,10 @@
         <v>32</v>
       </c>
       <c r="D108" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2907,10 +2940,10 @@
         <v>5</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E110" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E3FA3A-0F4A-45C8-AF4F-DDCD937DC092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199863DB-419A-4CE1-8F5C-593EABBC9FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="171">
   <si>
     <t>ModifierID</t>
   </si>
@@ -551,86 +551,6 @@
   </si>
   <si>
     <r>
-      <t>基</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>础</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>塔：每秒消耗1点MP</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>散射塔：每秒消耗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>点MP（加倍）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>减速塔：每秒消耗0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>点MP（减半）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>float_add|Reduce_MP_PerSecond|-</t>
     </r>
     <r>
@@ -685,12 +605,28 @@
     <t>CharacterHitTarget|DoDamage|DoHitCharacter|9999</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>散射塔：每秒消耗2点MP（加倍）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速塔：每秒消耗0.5点MP（减半）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础塔：每秒消耗1点MP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永久攻击力增加+5buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -716,16 +652,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -750,8 +678,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,12 +999,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F163EA-9459-48C1-AF83-EE818DD292D1}">
-  <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:E111"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="3" width="22.3984375" customWidth="1"/>
-    <col min="4" max="4" width="80.59765625" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" customWidth="1"/>
+    <col min="1" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="80.5546875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1089,7 +1020,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1106,7 +1037,7 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1123,7 +1054,7 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1140,7 +1071,7 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1157,7 +1088,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1174,7 +1105,7 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1191,7 +1122,7 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1208,7 +1139,7 @@
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1225,7 +1156,7 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1242,7 +1173,7 @@
       <c r="D10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1259,7 +1190,7 @@
       <c r="D11" t="s">
         <v>6</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1276,7 +1207,7 @@
       <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1293,7 +1224,7 @@
       <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1310,7 +1241,7 @@
       <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1327,7 +1258,7 @@
       <c r="D15" t="s">
         <v>35</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1344,7 +1275,7 @@
       <c r="D16" t="s">
         <v>37</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1361,7 +1292,7 @@
       <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1378,7 +1309,7 @@
       <c r="D18" t="s">
         <v>41</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1395,7 +1326,7 @@
       <c r="D19" t="s">
         <v>43</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1412,7 +1343,7 @@
       <c r="D20" t="s">
         <v>44</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1429,7 +1360,7 @@
       <c r="D21" t="s">
         <v>46</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1446,7 +1377,7 @@
       <c r="D22" t="s">
         <v>48</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1463,7 +1394,7 @@
       <c r="D23" t="s">
         <v>50</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1480,7 +1411,7 @@
       <c r="D24" t="s">
         <v>52</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1497,7 +1428,7 @@
       <c r="D25" t="s">
         <v>54</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1514,7 +1445,7 @@
       <c r="D26" t="s">
         <v>56</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1531,7 +1462,7 @@
       <c r="D27" t="s">
         <v>41</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1548,7 +1479,7 @@
       <c r="D28" t="s">
         <v>57</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1565,7 +1496,7 @@
       <c r="D29" t="s">
         <v>58</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1582,7 +1513,7 @@
       <c r="D30" t="s">
         <v>59</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1599,7 +1530,7 @@
       <c r="D31" t="s">
         <v>48</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1616,7 +1547,7 @@
       <c r="D32" t="s">
         <v>60</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1633,7 +1564,7 @@
       <c r="D33" t="s">
         <v>61</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1650,7 +1581,7 @@
       <c r="D34" t="s">
         <v>63</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1667,7 +1598,7 @@
       <c r="D35" t="s">
         <v>65</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1684,7 +1615,7 @@
       <c r="D36" t="s">
         <v>66</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1701,7 +1632,7 @@
       <c r="D37" t="s">
         <v>67</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1718,7 +1649,7 @@
       <c r="D38" t="s">
         <v>41</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1735,7 +1666,7 @@
       <c r="D39" t="s">
         <v>68</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1752,7 +1683,7 @@
       <c r="D40" t="s">
         <v>70</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1769,7 +1700,7 @@
       <c r="D41" t="s">
         <v>71</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1786,7 +1717,7 @@
       <c r="D42" t="s">
         <v>48</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1803,7 +1734,7 @@
       <c r="D43" t="s">
         <v>72</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1820,7 +1751,7 @@
       <c r="D44" t="s">
         <v>73</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1837,7 +1768,7 @@
       <c r="D45" t="s">
         <v>74</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1854,7 +1785,7 @@
       <c r="D46" t="s">
         <v>75</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1871,7 +1802,7 @@
       <c r="D47" t="s">
         <v>76</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1888,7 +1819,7 @@
       <c r="D48" t="s">
         <v>67</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1905,7 +1836,7 @@
       <c r="D49" t="s">
         <v>41</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1922,7 +1853,7 @@
       <c r="D50" t="s">
         <v>77</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1939,7 +1870,7 @@
       <c r="D51" t="s">
         <v>78</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1956,7 +1887,7 @@
       <c r="D52" t="s">
         <v>79</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1973,7 +1904,7 @@
       <c r="D53" t="s">
         <v>80</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1990,7 +1921,7 @@
       <c r="D54" t="s">
         <v>81</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2007,7 +1938,7 @@
       <c r="D55" t="s">
         <v>76</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2024,7 +1955,7 @@
       <c r="D56" t="s">
         <v>82</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2041,7 +1972,7 @@
       <c r="D57" t="s">
         <v>152</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2058,7 +1989,7 @@
       <c r="D58" t="s">
         <v>85</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2075,7 +2006,7 @@
       <c r="D59" t="s">
         <v>6</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2092,7 +2023,7 @@
       <c r="D60" t="s">
         <v>8</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2109,7 +2040,7 @@
       <c r="D61" t="s">
         <v>17</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2126,7 +2057,7 @@
       <c r="D62" t="s">
         <v>90</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2143,7 +2074,7 @@
       <c r="D63" t="s">
         <v>92</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2160,7 +2091,7 @@
       <c r="D64" t="s">
         <v>94</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2177,7 +2108,7 @@
       <c r="D65" t="s">
         <v>96</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2194,7 +2125,7 @@
       <c r="D66" t="s">
         <v>97</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2211,7 +2142,7 @@
       <c r="D67" t="s">
         <v>98</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2228,7 +2159,7 @@
       <c r="D68" t="s">
         <v>99</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2245,7 +2176,7 @@
       <c r="D69" t="s">
         <v>101</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2262,7 +2193,7 @@
       <c r="D70" t="s">
         <v>104</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2279,7 +2210,7 @@
       <c r="D71" t="s">
         <v>107</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2296,7 +2227,7 @@
       <c r="D72" t="s">
         <v>109</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2313,7 +2244,7 @@
       <c r="D73" t="s">
         <v>111</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2330,7 +2261,7 @@
       <c r="D74" t="s">
         <v>113</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2347,7 +2278,7 @@
       <c r="D75" t="s">
         <v>115</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2364,7 +2295,7 @@
       <c r="D76" t="s">
         <v>117</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2381,7 +2312,7 @@
       <c r="D77" t="s">
         <v>119</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2398,7 +2329,7 @@
       <c r="D78" t="s">
         <v>120</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2413,9 +2344,9 @@
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
-      </c>
-      <c r="E79" t="s">
+        <v>164</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2432,7 +2363,7 @@
       <c r="D80" t="s">
         <v>122</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2449,7 +2380,7 @@
       <c r="D81" t="s">
         <v>13</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2466,8 +2397,8 @@
       <c r="D82" t="s">
         <v>159</v>
       </c>
-      <c r="E82" t="s">
-        <v>162</v>
+      <c r="E82" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2483,11 +2414,11 @@
       <c r="D83" t="s">
         <v>124</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" ht="15.6">
       <c r="A84">
         <v>12002</v>
       </c>
@@ -2500,8 +2431,8 @@
       <c r="D84" t="s">
         <v>160</v>
       </c>
-      <c r="E84" t="s">
-        <v>163</v>
+      <c r="E84" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2517,11 +2448,11 @@
       <c r="D85" t="s">
         <v>158</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86">
         <v>12003</v>
       </c>
@@ -2534,8 +2465,8 @@
       <c r="D86" t="s">
         <v>161</v>
       </c>
-      <c r="E86" t="s">
-        <v>164</v>
+      <c r="E86" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2551,7 +2482,7 @@
       <c r="D87" t="s">
         <v>156</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2568,7 +2499,7 @@
       <c r="D88" t="s">
         <v>128</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2585,11 +2516,11 @@
       <c r="D89" t="s">
         <v>130</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90">
         <v>13001</v>
       </c>
@@ -2600,27 +2531,24 @@
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>165</v>
-      </c>
-      <c r="E90" t="s">
+        <v>162</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>14001</v>
+        <v>13002</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
-      </c>
-      <c r="D91" t="s">
-        <v>133</v>
-      </c>
-      <c r="E91" t="s">
-        <v>134</v>
+        <v>5</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2628,33 +2556,33 @@
         <v>14001</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
         <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>135</v>
-      </c>
-      <c r="E92" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>14002</v>
+        <v>14001</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="s">
         <v>32</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
-      </c>
-      <c r="E93" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2662,33 +2590,33 @@
         <v>14002</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="s">
         <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
-      </c>
-      <c r="E94" t="s">
-        <v>140</v>
+        <v>137</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>15001</v>
+        <v>14002</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D95" t="s">
-        <v>141</v>
-      </c>
-      <c r="E95" t="s">
-        <v>142</v>
+        <v>139</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2696,33 +2624,33 @@
         <v>15001</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>143</v>
-      </c>
-      <c r="E96" t="s">
-        <v>144</v>
+        <v>141</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>8002</v>
+        <v>15001</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
-      </c>
-      <c r="E97" t="s">
-        <v>114</v>
+        <v>143</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2730,16 +2658,16 @@
         <v>8002</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
-      </c>
-      <c r="E98" t="s">
-        <v>146</v>
+        <v>113</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2747,33 +2675,33 @@
         <v>8002</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C99" t="s">
         <v>32</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
-      </c>
-      <c r="E99" t="s">
-        <v>118</v>
+        <v>145</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
-      </c>
-      <c r="E100" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2781,67 +2709,67 @@
         <v>8003</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>168</v>
-      </c>
-      <c r="E101" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>113</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.6">
       <c r="A102">
         <v>8003</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102" t="s">
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
-      </c>
-      <c r="E102" t="s">
-        <v>118</v>
+        <v>165</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>12004</v>
+        <v>8003</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" t="s">
-        <v>148</v>
+        <v>166</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>16001</v>
+        <v>12004</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
-        <v>149</v>
-      </c>
-      <c r="E104" t="s">
-        <v>110</v>
+        <v>147</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2849,33 +2777,33 @@
         <v>16001</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" t="s">
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>157</v>
-      </c>
-      <c r="E105" t="s">
-        <v>112</v>
+        <v>149</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>16002</v>
+        <v>16001</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D106" t="s">
-        <v>150</v>
-      </c>
-      <c r="E106" t="s">
-        <v>114</v>
+        <v>157</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2883,16 +2811,16 @@
         <v>16002</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D107" t="s">
-        <v>151</v>
-      </c>
-      <c r="E107" t="s">
-        <v>116</v>
+        <v>150</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2900,16 +2828,16 @@
         <v>16002</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" t="s">
         <v>32</v>
       </c>
       <c r="D108" t="s">
-        <v>154</v>
-      </c>
-      <c r="E108" t="s">
-        <v>153</v>
+        <v>151</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2917,32 +2845,49 @@
         <v>16002</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" t="s">
         <v>32</v>
       </c>
       <c r="D109" t="s">
-        <v>117</v>
-      </c>
-      <c r="E109" t="s">
-        <v>118</v>
+        <v>154</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
+        <v>16002</v>
+      </c>
+      <c r="B110">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>32</v>
+      </c>
+      <c r="D110" t="s">
+        <v>117</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.6">
+      <c r="A111">
         <v>16003</v>
       </c>
-      <c r="B110">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
-        <v>5</v>
-      </c>
-      <c r="D110" t="s">
-        <v>166</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>163</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>155</v>
       </c>
     </row>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E3FA3A-0F4A-45C8-AF4F-DDCD937DC092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D1A0AF-A5DE-4209-87E8-9C0F5BFAADE3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13180" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -466,9 +466,6 @@
   </si>
   <si>
     <t>碰撞时造成18点伤害</t>
-  </si>
-  <si>
-    <t>int_set|Damage_Shoot|1</t>
   </si>
   <si>
     <t>设置防御塔攻击力为1</t>
@@ -593,7 +590,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -620,7 +617,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -685,23 +682,27 @@
     <t>CharacterHitTarget|DoDamage|DoHitCharacter|9999</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>int_set|Damage_Shoot|1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -772,9 +773,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -812,7 +813,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -918,7 +919,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1060,7 +1061,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1069,14 +1070,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F163EA-9459-48C1-AF83-EE818DD292D1}">
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="22.3984375" customWidth="1"/>
-    <col min="4" max="4" width="80.59765625" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" customWidth="1"/>
+    <col min="1" max="3" width="22.4140625" customWidth="1"/>
+    <col min="4" max="4" width="80.58203125" customWidth="1"/>
+    <col min="5" max="5" width="22.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1110,7 +1111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1144,7 +1145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1161,7 +1162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1178,7 +1179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1195,7 +1196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1229,7 +1230,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1246,7 +1247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1263,7 +1264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
@@ -1280,7 +1281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1297,7 +1298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -1314,7 +1315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -1331,7 +1332,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1001</v>
       </c>
@@ -1365,7 +1366,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1001</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1001</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1001</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1001</v>
       </c>
@@ -1433,7 +1434,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1467,7 +1468,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1001</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1001</v>
       </c>
@@ -1501,7 +1502,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1002</v>
       </c>
@@ -1518,7 +1519,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1002</v>
       </c>
@@ -1535,7 +1536,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1002</v>
       </c>
@@ -1552,7 +1553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1002</v>
       </c>
@@ -1569,7 +1570,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1002</v>
       </c>
@@ -1586,7 +1587,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1002</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1002</v>
       </c>
@@ -1620,7 +1621,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1002</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1002</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1671,7 +1672,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1003</v>
       </c>
@@ -1705,7 +1706,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1003</v>
       </c>
@@ -1722,7 +1723,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1003</v>
       </c>
@@ -1739,7 +1740,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1003</v>
       </c>
@@ -1756,7 +1757,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1003</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1003</v>
       </c>
@@ -1790,7 +1791,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1003</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1003</v>
       </c>
@@ -1824,7 +1825,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1003</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1003</v>
       </c>
@@ -1858,7 +1859,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1003</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1004</v>
       </c>
@@ -1892,7 +1893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1004</v>
       </c>
@@ -1909,7 +1910,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1004</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1004</v>
       </c>
@@ -1943,7 +1944,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1004</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1004</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1004</v>
       </c>
@@ -2011,7 +2012,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>3001</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>3001</v>
       </c>
@@ -2039,13 +2040,13 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E57" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>3001</v>
       </c>
@@ -2062,7 +2063,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>3002</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>3002</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>3002</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>4001</v>
       </c>
@@ -2130,7 +2131,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>4001</v>
       </c>
@@ -2147,7 +2148,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>4002</v>
       </c>
@@ -2164,7 +2165,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>4002</v>
       </c>
@@ -2181,7 +2182,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>4002</v>
       </c>
@@ -2198,7 +2199,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>4002</v>
       </c>
@@ -2215,7 +2216,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>5001</v>
       </c>
@@ -2232,7 +2233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>5001</v>
       </c>
@@ -2249,7 +2250,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>6001</v>
       </c>
@@ -2266,7 +2267,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>6001</v>
       </c>
@@ -2283,7 +2284,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>7001</v>
       </c>
@@ -2300,7 +2301,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>7001</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8001</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8001</v>
       </c>
@@ -2351,7 +2352,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8001</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>9001</v>
       </c>
@@ -2385,7 +2386,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9001</v>
       </c>
@@ -2402,7 +2403,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>10001</v>
       </c>
@@ -2413,13 +2414,13 @@
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E79" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>10001</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>11001</v>
       </c>
@@ -2453,7 +2454,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>12001</v>
       </c>
@@ -2464,13 +2465,13 @@
         <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E82" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>12001</v>
       </c>
@@ -2487,7 +2488,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>12002</v>
       </c>
@@ -2498,13 +2499,13 @@
         <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E84" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>12002</v>
       </c>
@@ -2515,13 +2516,13 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E85" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>12003</v>
       </c>
@@ -2532,13 +2533,13 @@
         <v>5</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E86" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>12003</v>
       </c>
@@ -2549,13 +2550,13 @@
         <v>5</v>
       </c>
       <c r="D87" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E87" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>13001</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>13001</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>13001</v>
       </c>
@@ -2600,13 +2601,13 @@
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E90" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>14001</v>
       </c>
@@ -2623,7 +2624,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>14001</v>
       </c>
@@ -2640,7 +2641,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>14002</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>14002</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>15001</v>
       </c>
@@ -2691,7 +2692,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>15001</v>
       </c>
@@ -2708,7 +2709,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>8002</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>8002</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>8002</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>8003</v>
       </c>
@@ -2776,7 +2777,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>8003</v>
       </c>
@@ -2787,13 +2788,13 @@
         <v>32</v>
       </c>
       <c r="D101" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E101" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>8003</v>
       </c>
@@ -2804,13 +2805,13 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E102" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>12004</v>
       </c>
@@ -2821,13 +2822,13 @@
         <v>5</v>
       </c>
       <c r="D103" t="s">
+        <v>169</v>
+      </c>
+      <c r="E103" t="s">
         <v>147</v>
       </c>
-      <c r="E103" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>16001</v>
       </c>
@@ -2838,13 +2839,13 @@
         <v>32</v>
       </c>
       <c r="D104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E104" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>16001</v>
       </c>
@@ -2855,13 +2856,13 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>16002</v>
       </c>
@@ -2872,13 +2873,13 @@
         <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E106" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>16002</v>
       </c>
@@ -2889,13 +2890,13 @@
         <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E107" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>16002</v>
       </c>
@@ -2906,13 +2907,13 @@
         <v>32</v>
       </c>
       <c r="D108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E108" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>16002</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>16003</v>
       </c>
@@ -2940,10 +2941,10 @@
         <v>5</v>
       </c>
       <c r="D110" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameModifiers.xlsx
+++ b/Assets/Configs/GameModifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199863DB-419A-4CE1-8F5C-593EABBC9FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F685E0EB-1E80-4591-A2CC-3E928AFE6894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{478B3112-DF2F-4443-9DAF-B778DD3194E3}"/>
   </bookViews>
@@ -462,12 +462,6 @@
     <t>减速Buff：绑定减速特效</t>
   </si>
   <si>
-    <t>CharacterHitTarget|DoDamage|BeHitCharacter|18</t>
-  </si>
-  <si>
-    <t>碰撞时造成18点伤害</t>
-  </si>
-  <si>
     <t>int_set|Damage_Shoot|1</t>
   </si>
   <si>
@@ -518,107 +512,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>float_add|Reduce_MP_PerSecond|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>float_add|Reduce_MP_PerSecond|0.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>float_add|Reduce_MP_PerSecond|-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>50</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>float_add|MaxSpeed|-0.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterCastSkill|DropCurObject|MainCharacter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>CharacterHitTarget|DoDamage|BeHitCharacter|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>36</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterHitTarget|DoDamage|DoHitCharacter|9999</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>散射塔：每秒消耗2点MP（加倍）</t>
+    <t>永久攻击力增加+5buff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>减速塔：每秒消耗0.5点MP（减半）</t>
+    <t>基础塔：每秒消耗1.25点MP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基础塔：每秒消耗1点MP</t>
+    <t>散射塔：每秒消耗2.5点MP（加倍）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>永久攻击力增加+5buff</t>
+    <t>减速塔：每秒消耗1点MP（减半）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰撞时造成15点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰撞时造成10点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|Reduce_MP_PerSecond|1.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|Reduce_MP_PerSecond|2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|Reduce_MP_PerSecond|-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float_add|MaxSpeed|-0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterHitTarget|DoDamage|BeHitCharacter|10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -626,7 +568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -641,13 +583,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -682,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,11 +935,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F163EA-9459-48C1-AF83-EE818DD292D1}">
   <dimension ref="A1:E111"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="3" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="80.5546875" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="22.3984375" customWidth="1"/>
+    <col min="4" max="4" width="80.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.3984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1017,7 +952,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1034,7 +969,7 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1051,7 +986,7 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1068,7 +1003,7 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1085,7 +1020,7 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1102,7 +1037,7 @@
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1119,7 +1054,7 @@
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1136,7 +1071,7 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1153,7 +1088,7 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1170,7 +1105,7 @@
       <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1187,7 +1122,7 @@
       <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1204,7 +1139,7 @@
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1221,7 +1156,7 @@
       <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1238,7 +1173,7 @@
       <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1255,7 +1190,7 @@
       <c r="C15" t="s">
         <v>12</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1272,7 +1207,7 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1289,7 +1224,7 @@
       <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1306,7 +1241,7 @@
       <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1323,7 +1258,7 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1340,7 +1275,7 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1357,7 +1292,7 @@
       <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1374,7 +1309,7 @@
       <c r="C22" t="s">
         <v>32</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1391,7 +1326,7 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1408,7 +1343,7 @@
       <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1425,7 +1360,7 @@
       <c r="C25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1442,7 +1377,7 @@
       <c r="C26" t="s">
         <v>5</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1459,7 +1394,7 @@
       <c r="C27" t="s">
         <v>5</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1476,7 +1411,7 @@
       <c r="C28" t="s">
         <v>5</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -1493,7 +1428,7 @@
       <c r="C29" t="s">
         <v>5</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1510,7 +1445,7 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1527,7 +1462,7 @@
       <c r="C31" t="s">
         <v>32</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1544,7 +1479,7 @@
       <c r="C32" t="s">
         <v>32</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1561,7 +1496,7 @@
       <c r="C33" t="s">
         <v>32</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1578,7 +1513,7 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1595,7 +1530,7 @@
       <c r="C35" t="s">
         <v>32</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1612,7 +1547,7 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -1629,7 +1564,7 @@
       <c r="C37" t="s">
         <v>5</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -1646,7 +1581,7 @@
       <c r="C38" t="s">
         <v>5</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -1663,7 +1598,7 @@
       <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1680,7 +1615,7 @@
       <c r="C40" t="s">
         <v>5</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -1697,7 +1632,7 @@
       <c r="C41" t="s">
         <v>32</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -1714,7 +1649,7 @@
       <c r="C42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -1731,7 +1666,7 @@
       <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -1748,7 +1683,7 @@
       <c r="C44" t="s">
         <v>32</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -1765,7 +1700,7 @@
       <c r="C45" t="s">
         <v>32</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -1782,7 +1717,7 @@
       <c r="C46" t="s">
         <v>32</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -1799,7 +1734,7 @@
       <c r="C47" t="s">
         <v>32</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -1816,7 +1751,7 @@
       <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -1833,7 +1768,7 @@
       <c r="C49" t="s">
         <v>5</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -1850,7 +1785,7 @@
       <c r="C50" t="s">
         <v>5</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>77</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -1867,7 +1802,7 @@
       <c r="C51" t="s">
         <v>5</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1884,7 +1819,7 @@
       <c r="C52" t="s">
         <v>32</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1901,7 +1836,7 @@
       <c r="C53" t="s">
         <v>32</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -1918,7 +1853,7 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -1935,7 +1870,7 @@
       <c r="C55" t="s">
         <v>32</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -1952,7 +1887,7 @@
       <c r="C56" t="s">
         <v>32</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -1969,8 +1904,8 @@
       <c r="C57" t="s">
         <v>32</v>
       </c>
-      <c r="D57" t="s">
-        <v>152</v>
+      <c r="D57" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>84</v>
@@ -1986,7 +1921,7 @@
       <c r="C58" t="s">
         <v>32</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -2003,7 +1938,7 @@
       <c r="C59" t="s">
         <v>5</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -2020,7 +1955,7 @@
       <c r="C60" t="s">
         <v>5</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -2037,7 +1972,7 @@
       <c r="C61" t="s">
         <v>5</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -2054,7 +1989,7 @@
       <c r="C62" t="s">
         <v>32</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -2071,7 +2006,7 @@
       <c r="C63" t="s">
         <v>32</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -2088,7 +2023,7 @@
       <c r="C64" t="s">
         <v>93</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -2105,7 +2040,7 @@
       <c r="C65" t="s">
         <v>93</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -2122,7 +2057,7 @@
       <c r="C66" t="s">
         <v>93</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -2139,7 +2074,7 @@
       <c r="C67" t="s">
         <v>32</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2156,7 +2091,7 @@
       <c r="C68" t="s">
         <v>32</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -2173,7 +2108,7 @@
       <c r="C69" t="s">
         <v>32</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -2190,7 +2125,7 @@
       <c r="C70" t="s">
         <v>103</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -2207,7 +2142,7 @@
       <c r="C71" t="s">
         <v>106</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -2224,7 +2159,7 @@
       <c r="C72" t="s">
         <v>32</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -2241,7 +2176,7 @@
       <c r="C73" t="s">
         <v>32</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -2258,7 +2193,7 @@
       <c r="C74" t="s">
         <v>5</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -2275,7 +2210,7 @@
       <c r="C75" t="s">
         <v>32</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>115</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -2292,7 +2227,7 @@
       <c r="C76" t="s">
         <v>32</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -2309,7 +2244,7 @@
       <c r="C77" t="s">
         <v>32</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -2326,7 +2261,7 @@
       <c r="C78" t="s">
         <v>32</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>120</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -2343,8 +2278,8 @@
       <c r="C79" t="s">
         <v>32</v>
       </c>
-      <c r="D79" t="s">
-        <v>164</v>
+      <c r="D79" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>121</v>
@@ -2360,7 +2295,7 @@
       <c r="C80" t="s">
         <v>32</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>122</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -2377,7 +2312,7 @@
       <c r="C81" t="s">
         <v>12</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -2394,11 +2329,11 @@
       <c r="C82" t="s">
         <v>5</v>
       </c>
-      <c r="D82" t="s">
-        <v>159</v>
+      <c r="D82" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2411,14 +2346,14 @@
       <c r="C83" t="s">
         <v>5</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.6">
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>12002</v>
       </c>
@@ -2428,11 +2363,11 @@
       <c r="C84" t="s">
         <v>5</v>
       </c>
-      <c r="D84" t="s">
-        <v>160</v>
+      <c r="D84" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2445,14 +2380,14 @@
       <c r="C85" t="s">
         <v>5</v>
       </c>
-      <c r="D85" t="s">
-        <v>158</v>
+      <c r="D85" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>12003</v>
       </c>
@@ -2462,11 +2397,11 @@
       <c r="C86" t="s">
         <v>5</v>
       </c>
-      <c r="D86" t="s">
-        <v>161</v>
+      <c r="D86" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2479,8 +2414,8 @@
       <c r="C87" t="s">
         <v>5</v>
       </c>
-      <c r="D87" t="s">
-        <v>156</v>
+      <c r="D87" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>127</v>
@@ -2496,7 +2431,7 @@
       <c r="C88" t="s">
         <v>32</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -2513,14 +2448,14 @@
       <c r="C89" t="s">
         <v>32</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>13001</v>
       </c>
@@ -2530,8 +2465,8 @@
       <c r="C90" t="s">
         <v>5</v>
       </c>
-      <c r="D90" t="s">
-        <v>162</v>
+      <c r="D90" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>132</v>
@@ -2548,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2561,7 +2496,7 @@
       <c r="C92" t="s">
         <v>32</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -2578,7 +2513,7 @@
       <c r="C93" t="s">
         <v>32</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -2595,7 +2530,7 @@
       <c r="C94" t="s">
         <v>32</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -2612,7 +2547,7 @@
       <c r="C95" t="s">
         <v>32</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -2629,7 +2564,7 @@
       <c r="C96" t="s">
         <v>5</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -2646,7 +2581,7 @@
       <c r="C97" t="s">
         <v>12</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -2663,7 +2598,7 @@
       <c r="C98" t="s">
         <v>5</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -2680,11 +2615,11 @@
       <c r="C99" t="s">
         <v>32</v>
       </c>
-      <c r="D99" t="s">
-        <v>145</v>
+      <c r="D99" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2697,7 +2632,7 @@
       <c r="C100" t="s">
         <v>32</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -2714,14 +2649,14 @@
       <c r="C101" t="s">
         <v>5</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15.6">
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>8003</v>
       </c>
@@ -2731,11 +2666,11 @@
       <c r="C102" t="s">
         <v>32</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2748,8 +2683,8 @@
       <c r="C103" t="s">
         <v>32</v>
       </c>
-      <c r="D103" t="s">
-        <v>166</v>
+      <c r="D103" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>118</v>
@@ -2765,11 +2700,11 @@
       <c r="C104" t="s">
         <v>5</v>
       </c>
-      <c r="D104" t="s">
-        <v>147</v>
+      <c r="D104" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2782,8 +2717,8 @@
       <c r="C105" t="s">
         <v>32</v>
       </c>
-      <c r="D105" t="s">
-        <v>149</v>
+      <c r="D105" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>110</v>
@@ -2799,8 +2734,8 @@
       <c r="C106" t="s">
         <v>32</v>
       </c>
-      <c r="D106" t="s">
-        <v>157</v>
+      <c r="D106" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>112</v>
@@ -2816,8 +2751,8 @@
       <c r="C107" t="s">
         <v>5</v>
       </c>
-      <c r="D107" t="s">
-        <v>150</v>
+      <c r="D107" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>114</v>
@@ -2833,8 +2768,8 @@
       <c r="C108" t="s">
         <v>32</v>
       </c>
-      <c r="D108" t="s">
-        <v>151</v>
+      <c r="D108" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>116</v>
@@ -2850,11 +2785,11 @@
       <c r="C109" t="s">
         <v>32</v>
       </c>
-      <c r="D109" t="s">
-        <v>154</v>
+      <c r="D109" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2867,14 +2802,14 @@
       <c r="C110" t="s">
         <v>32</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15.6">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>16003</v>
       </c>
@@ -2884,11 +2819,11 @@
       <c r="C111" t="s">
         <v>5</v>
       </c>
-      <c r="D111" t="s">
-        <v>163</v>
+      <c r="D111" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
